--- a/artfynd/A 2165-2022 artfynd.xlsx
+++ b/artfynd/A 2165-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 2165-2022 artfynd.xlsx
+++ b/artfynd/A 2165-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1258,10 +1258,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>107401720</v>
+        <v>118169898</v>
       </c>
       <c r="B7" t="n">
-        <v>96226</v>
+        <v>97821</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1270,30 +1270,30 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>290</v>
+        <v>219797</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Röd skogslilja</t>
+          <t>Purpurknipprot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cephalanthera rubra</t>
+          <t>Epipactis atrorubens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Hoffm.) Besser</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>75</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1306,16 +1306,18 @@
           <t>blomning</t>
         </is>
       </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>NV Skärblacka, Ög</t>
+          <t>Berggården SSO 400 m, Ög</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>551386.1544718138</v>
+        <v>551376</v>
       </c>
       <c r="R7" t="n">
-        <v>6493839.207874644</v>
+        <v>6493848</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1340,29 +1342,19 @@
           <t>Kullerstad</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>E-Nor-0726</t>
-        </is>
-      </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2011-06-16</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2011-06-16</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-07-01</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>50-100 plantor</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1371,154 +1363,27 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Blandskog</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Monika Sunhede</t>
+          <t>Mirjam Ideström</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Maria Taberman</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>118169898</v>
-      </c>
-      <c r="B8" t="n">
-        <v>97821</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>219797</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Purpurknipprot</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Epipactis atrorubens</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>(Hoffm.) Besser</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>Berggården SSO 400 m, Ög</t>
-        </is>
-      </c>
-      <c r="Q8" t="n">
-        <v>551376</v>
-      </c>
-      <c r="R8" t="n">
-        <v>6493848</v>
-      </c>
-      <c r="S8" t="n">
-        <v>50</v>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>Östergötland</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>Norrköping</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>Östergötland</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>Kullerstad</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>2024-07-01</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>2024-07-01</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>50-100 plantor</t>
-        </is>
-      </c>
-      <c r="AD8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF8" t="inlineStr"/>
-      <c r="AG8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Blandskog</t>
-        </is>
-      </c>
-      <c r="AT8" t="inlineStr"/>
-      <c r="AW8" t="inlineStr">
-        <is>
-          <t>Mirjam Ideström</t>
-        </is>
-      </c>
-      <c r="AX8" t="inlineStr">
-        <is>
           <t>Mirjam Ideström, Jan-Erik Axelsson</t>
         </is>
       </c>
-      <c r="AY8" t="inlineStr"/>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 2165-2022 artfynd.xlsx
+++ b/artfynd/A 2165-2022 artfynd.xlsx
@@ -675,55 +675,62 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>98587805</v>
+        <v>6772561</v>
       </c>
       <c r="B2" t="n">
-        <v>93158</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99011</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2818</v>
+        <v>290</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Röd skogslilja</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Cephalanthera rubra</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Norrköping, Ög</t>
+          <t>NV Skärblacka, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>551144.6679380166</v>
+        <v>551386</v>
       </c>
       <c r="R2" t="n">
-        <v>6494128.559999075</v>
+        <v>6493839</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -747,22 +754,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-02-12</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2011-06-16</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-02-12</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2011-06-16</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,12 +774,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Rasmus Viding</t>
+          <t>Maria Taberman</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Rasmus Viding, Nina Marliden, David Ek</t>
+          <t>Maria Taberman</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -792,12 +789,7 @@
         <v>98587777</v>
       </c>
       <c r="B3" t="n">
-        <v>93158</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96458</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -831,10 +823,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>551137.9056452526</v>
+        <v>551138</v>
       </c>
       <c r="R3" t="n">
-        <v>6494126.385744419</v>
+        <v>6494126</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -864,19 +856,9 @@
           <t>2022-02-12</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-02-12</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -903,15 +885,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>98587928</v>
+        <v>98587805</v>
       </c>
       <c r="B4" t="n">
-        <v>4717</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96458</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -919,37 +896,36 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102306</v>
+        <v>2818</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Norrköping, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>551193.9466789172</v>
+        <v>551145</v>
       </c>
       <c r="R4" t="n">
-        <v>6494115.127848891</v>
+        <v>6494128</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -979,19 +955,9 @@
           <t>2022-02-12</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-02-12</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,22 +977,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Rasmus Viding, David Ek</t>
+          <t>Rasmus Viding, Nina Marliden, David Ek</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>98587953</v>
+        <v>98587928</v>
       </c>
       <c r="B5" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>4781</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1034,36 +995,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
+        <v>102306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Norrköping, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>551177.926892556</v>
+        <v>551194</v>
       </c>
       <c r="R5" t="n">
-        <v>6494101.882375493</v>
+        <v>6494115</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1093,19 +1055,9 @@
           <t>2022-02-12</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-02-12</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1125,49 +1077,44 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Rasmus Viding, Nina Marliden</t>
+          <t>Rasmus Viding, David Ek</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>6772561</v>
+        <v>118169898</v>
       </c>
       <c r="B6" t="n">
-        <v>96226</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>99093</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>290</v>
+        <v>219797</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Röd skogslilja</t>
+          <t>Purpurknipprot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cephalanthera rubra</t>
+          <t>Epipactis atrorubens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Hoffm.) Besser</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>75</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1180,16 +1127,18 @@
           <t>blomning</t>
         </is>
       </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>NV Skärblacka, Ög</t>
+          <t>Berggården SSO 400 m, Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>551386.1613349434</v>
+        <v>551376</v>
       </c>
       <c r="R6" t="n">
-        <v>6493838.686512573</v>
+        <v>6493848</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1216,22 +1165,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2011-06-16</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2011-06-16</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-07-01</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>50-100 plantor</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1240,33 +1184,34 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Blandskog</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Maria Taberman</t>
+          <t>Mirjam Ideström</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Maria Taberman</t>
+          <t>Mirjam Ideström, Jan-Erik Axelsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118169898</v>
+        <v>98587953</v>
       </c>
       <c r="B7" t="n">
-        <v>97821</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1274,53 +1219,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219797</v>
+        <v>222498</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Purpurknipprot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Epipactis atrorubens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hoffm.) Besser</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Berggården SSO 400 m, Ög</t>
+          <t>Norrköping, Ög</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>551376</v>
+        <v>551178</v>
       </c>
       <c r="R7" t="n">
-        <v>6493848</v>
+        <v>6494101</v>
       </c>
       <c r="S7" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1344,17 +1275,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
+          <t>2022-02-12</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>50-100 plantor</t>
+          <t>2022-02-12</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1363,24 +1289,18 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Blandskog</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Mirjam Ideström</t>
+          <t>Rasmus Viding</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Mirjam Ideström, Jan-Erik Axelsson</t>
+          <t>Rasmus Viding, Nina Marliden</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>

--- a/artfynd/A 2165-2022 artfynd.xlsx
+++ b/artfynd/A 2165-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -771,6 +776,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98587777</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -870,6 +880,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98587805</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -970,6 +985,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98587928</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1069,6 +1089,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98587953</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1180,6 +1205,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6772561</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1304,8 +1334,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118169898</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>